--- a/student_leaders_to_leaders.xlsx
+++ b/student_leaders_to_leaders.xlsx
@@ -483,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
@@ -509,7 +509,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>152</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>101</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
